--- a/Timetables.xlsx
+++ b/Timetables.xlsx
@@ -155,7 +155,7 @@
     <t>15/09/2026</t>
   </si>
   <si>
-    <t>GLA.SA105</t>
+    <t>GLA.HG20</t>
   </si>
   <si>
     <t>2</t>
